--- a/artfynd/A 9583-2022 artfynd.xlsx
+++ b/artfynd/A 9583-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113507747</v>
+        <v>113507746</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>79218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551114</v>
+        <v>551104</v>
       </c>
       <c r="R2" t="n">
-        <v>7037152</v>
+        <v>7037160</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113507746</v>
+        <v>113507747</v>
       </c>
       <c r="B3" t="n">
-        <v>79196</v>
+        <v>78155</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551104</v>
+        <v>551114</v>
       </c>
       <c r="R3" t="n">
-        <v>7037160</v>
+        <v>7037152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 9583-2022 artfynd.xlsx
+++ b/artfynd/A 9583-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113507746</v>
+        <v>113507747</v>
       </c>
       <c r="B2" t="n">
-        <v>79218</v>
+        <v>78158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551104</v>
+        <v>551114</v>
       </c>
       <c r="R2" t="n">
-        <v>7037160</v>
+        <v>7037152</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113507747</v>
+        <v>113507746</v>
       </c>
       <c r="B3" t="n">
-        <v>78155</v>
+        <v>79222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551114</v>
+        <v>551104</v>
       </c>
       <c r="R3" t="n">
-        <v>7037152</v>
+        <v>7037160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 9583-2022 artfynd.xlsx
+++ b/artfynd/A 9583-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113507747</v>
+        <v>113507746</v>
       </c>
       <c r="B2" t="n">
-        <v>78158</v>
+        <v>79228</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551114</v>
+        <v>551104</v>
       </c>
       <c r="R2" t="n">
-        <v>7037152</v>
+        <v>7037160</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113507746</v>
+        <v>113507747</v>
       </c>
       <c r="B3" t="n">
-        <v>79222</v>
+        <v>78164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551104</v>
+        <v>551114</v>
       </c>
       <c r="R3" t="n">
-        <v>7037160</v>
+        <v>7037152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 9583-2022 artfynd.xlsx
+++ b/artfynd/A 9583-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113507746</v>
+        <v>113507747</v>
       </c>
       <c r="B2" t="n">
-        <v>79228</v>
+        <v>78164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551104</v>
+        <v>551114</v>
       </c>
       <c r="R2" t="n">
-        <v>7037160</v>
+        <v>7037152</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113507747</v>
+        <v>113507746</v>
       </c>
       <c r="B3" t="n">
-        <v>78164</v>
+        <v>79228</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551114</v>
+        <v>551104</v>
       </c>
       <c r="R3" t="n">
-        <v>7037152</v>
+        <v>7037160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 9583-2022 artfynd.xlsx
+++ b/artfynd/A 9583-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113507747</v>
       </c>
       <c r="B2" t="n">
-        <v>78164</v>
+        <v>78171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113507746</v>
       </c>
       <c r="B3" t="n">
-        <v>79228</v>
+        <v>79235</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9583-2022 artfynd.xlsx
+++ b/artfynd/A 9583-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113507747</v>
+        <v>113507746</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>79237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551114</v>
+        <v>551104</v>
       </c>
       <c r="R2" t="n">
-        <v>7037152</v>
+        <v>7037160</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113507746</v>
+        <v>113507747</v>
       </c>
       <c r="B3" t="n">
-        <v>79235</v>
+        <v>78173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551104</v>
+        <v>551114</v>
       </c>
       <c r="R3" t="n">
-        <v>7037160</v>
+        <v>7037152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 9583-2022 artfynd.xlsx
+++ b/artfynd/A 9583-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113507746</v>
+        <v>113507747</v>
       </c>
       <c r="B2" t="n">
-        <v>79237</v>
+        <v>78201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551104</v>
+        <v>551114</v>
       </c>
       <c r="R2" t="n">
-        <v>7037160</v>
+        <v>7037152</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113507747</v>
+        <v>113507746</v>
       </c>
       <c r="B3" t="n">
-        <v>78173</v>
+        <v>79265</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551114</v>
+        <v>551104</v>
       </c>
       <c r="R3" t="n">
-        <v>7037152</v>
+        <v>7037160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 9583-2022 artfynd.xlsx
+++ b/artfynd/A 9583-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113507747</v>
+        <v>113507746</v>
       </c>
       <c r="B2" t="n">
-        <v>78201</v>
+        <v>79265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551114</v>
+        <v>551104</v>
       </c>
       <c r="R2" t="n">
-        <v>7037152</v>
+        <v>7037160</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113507746</v>
+        <v>113507747</v>
       </c>
       <c r="B3" t="n">
-        <v>79265</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551104</v>
+        <v>551114</v>
       </c>
       <c r="R3" t="n">
-        <v>7037160</v>
+        <v>7037152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 9583-2022 artfynd.xlsx
+++ b/artfynd/A 9583-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113507746</v>
+        <v>113507747</v>
       </c>
       <c r="B2" t="n">
-        <v>79265</v>
+        <v>78201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551104</v>
+        <v>551114</v>
       </c>
       <c r="R2" t="n">
-        <v>7037160</v>
+        <v>7037152</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113507747</v>
+        <v>113507746</v>
       </c>
       <c r="B3" t="n">
-        <v>78201</v>
+        <v>79265</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551114</v>
+        <v>551104</v>
       </c>
       <c r="R3" t="n">
-        <v>7037152</v>
+        <v>7037160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 9583-2022 artfynd.xlsx
+++ b/artfynd/A 9583-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9583-2022 artfynd.xlsx
+++ b/artfynd/A 9583-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113507746</v>
+        <v>113507747</v>
       </c>
       <c r="B2" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551104</v>
+        <v>551114</v>
       </c>
       <c r="R2" t="n">
-        <v>7037160</v>
+        <v>7037152</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113507747</v>
+        <v>113507746</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551114</v>
+        <v>551104</v>
       </c>
       <c r="R3" t="n">
-        <v>7037152</v>
+        <v>7037160</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 9583-2022 artfynd.xlsx
+++ b/artfynd/A 9583-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113507747</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,8 +884,17 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113507746</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>